--- a/_proyecto/Registro_Negocios.xlsx
+++ b/_proyecto/Registro_Negocios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecnalia365-my.sharepoint.com/personal/inigo_arana_tecnalia_com/Documents/Escritorio/Personal/Cursor_Web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4710" documentId="11_180DE2EEB12A76AE30F8224BFABDEE52E13E727D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA14AA26-8DE6-4EA1-94D0-493427484BD5}"/>
+  <xr:revisionPtr revIDLastSave="4744" documentId="11_180DE2EEB12A76AE30F8224BFABDEE52E13E727D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2797C0C-6C48-4DB2-9587-481A429BD38D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2022,21 +2022,12 @@
     <t>http://www.laciadelron.com/</t>
   </si>
   <si>
-    <t>laciadelron.com (contenido ajeno/hijack); Instagram @la_compania_del_ron; tel. 944 024 844</t>
-  </si>
-  <si>
     <t>Bar copas/ron referencia Indautxu; prensa y redes activas.</t>
   </si>
   <si>
-    <t>Dominio histórico no muestra el negocio (contenido spam); sin carta propia.</t>
-  </si>
-  <si>
     <t>Recuperación dominio + vitrina ron/pintxos (rol 4: tardeo/catas).</t>
   </si>
   <si>
-    <t>https://laciadelron.com/ | https://www.deia.eus/gastronomia/2025/03/02/museo-ron-bilbao-9333821.html</t>
-  </si>
-  <si>
     <t>expedientes/0050_CompaniaDelRon</t>
   </si>
   <si>
@@ -2362,6 +2353,15 @@
   </si>
   <si>
     <t>Completado</t>
+  </si>
+  <si>
+    <t>laciadelron.com (hijack/spam); Instagram @la_compania_del_ron; Facebook Laciadelron22; Google 643802270; tel. hist. 944024844</t>
+  </si>
+  <si>
+    <t>Dominio histórico con contenido ajeno; sin carta propia; teléfonos discordantes en fuentes.</t>
+  </si>
+  <si>
+    <t>https://laciadelron.com/ | https://www.instagram.com/la_compania_del_ron/ | expedientes/0050_CompaniaDelRon/04-alcance-aceptado.json</t>
   </si>
 </sst>
 </file>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="H4" s="1">
         <f>COUNTIFS(AC7:AC206,"Seleccionado",A7:A206,"&lt;&gt;")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1" t="s">
@@ -5873,10 +5873,10 @@
         <v>329</v>
       </c>
       <c r="W25" s="7" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="X25" s="7" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="Y25" s="7" t="s">
         <v>118</v>
@@ -5913,7 +5913,7 @@
         <v>6</v>
       </c>
       <c r="AK25" s="7" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="AL25" s="10">
         <f>IF(OR(A25="",COUNT(AF25:AJ25)&lt;5),"",ROUND(SUMPRODUCT(AF25:AJ25,Guia!$B$7:$F$7),1))</f>
@@ -8922,10 +8922,10 @@
         <v>257</v>
       </c>
       <c r="AD47" s="7" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="AE47" s="7" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="AF47" s="9">
         <v>9</v>
@@ -8943,7 +8943,7 @@
         <v>8</v>
       </c>
       <c r="AK47" s="7" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="AL47" s="10">
         <f>IF(OR(A47="",COUNT(AF47:AJ47)&lt;5),"",ROUND(SUMPRODUCT(AF47:AJ47,Guia!$B$7:$F$7),1))</f>
@@ -8953,7 +8953,7 @@
         <v>8</v>
       </c>
       <c r="AN47" s="10" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="AO47" s="7" t="s">
         <v>122</v>
@@ -10141,35 +10141,35 @@
         <v>165</v>
       </c>
       <c r="U56" s="7" t="s">
+        <v>773</v>
+      </c>
+      <c r="V56" s="7" t="s">
         <v>662</v>
       </c>
-      <c r="V56" s="7" t="s">
+      <c r="W56" s="7" t="s">
+        <v>774</v>
+      </c>
+      <c r="X56" s="7" t="s">
         <v>663</v>
-      </c>
-      <c r="W56" s="7" t="s">
-        <v>664</v>
-      </c>
-      <c r="X56" s="7" t="s">
-        <v>665</v>
       </c>
       <c r="Y56" s="7" t="s">
         <v>162</v>
       </c>
       <c r="Z56" s="7" t="s">
-        <v>666</v>
+        <v>775</v>
       </c>
       <c r="AA56" s="16">
         <v>46293</v>
       </c>
       <c r="AB56" s="7" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="AC56" s="7" t="s">
-        <v>98</v>
+        <v>257</v>
       </c>
       <c r="AD56" s="7"/>
       <c r="AE56" s="7" t="s">
-        <v>120</v>
+        <v>259</v>
       </c>
       <c r="AF56" s="9">
         <v>8</v>
@@ -10187,7 +10187,7 @@
         <v>7</v>
       </c>
       <c r="AK56" s="7" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="AL56" s="10">
         <f>IF(OR(A56="",COUNT(AF56:AJ56)&lt;5),"",ROUND(SUMPRODUCT(AF56:AJ56,Guia!$B$7:$F$7),1))</f>
@@ -10199,13 +10199,13 @@
         <v>122</v>
       </c>
       <c r="AP56" s="7" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="AQ56" s="7" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="AR56" s="7" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="AS56" s="7" t="s">
         <v>97</v>
@@ -10219,28 +10219,28 @@
     </row>
     <row r="57" spans="1:47" ht="32" customHeight="1">
       <c r="A57" s="7" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>297</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="G57" s="7" t="s">
         <v>105</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="I57" s="7" t="s">
         <v>107</v>
@@ -10252,7 +10252,7 @@
         <v>210</v>
       </c>
       <c r="L57" s="7" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="M57" s="7" t="s">
         <v>111</v>
@@ -10279,28 +10279,28 @@
         <v>165</v>
       </c>
       <c r="U57" s="7" t="s">
+        <v>676</v>
+      </c>
+      <c r="V57" s="7" t="s">
+        <v>677</v>
+      </c>
+      <c r="W57" s="7" t="s">
+        <v>678</v>
+      </c>
+      <c r="X57" s="7" t="s">
         <v>679</v>
-      </c>
-      <c r="V57" s="7" t="s">
-        <v>680</v>
-      </c>
-      <c r="W57" s="7" t="s">
-        <v>681</v>
-      </c>
-      <c r="X57" s="7" t="s">
-        <v>682</v>
       </c>
       <c r="Y57" s="7" t="s">
         <v>118</v>
       </c>
       <c r="Z57" s="7" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="AA57" s="16">
         <v>46293</v>
       </c>
       <c r="AB57" s="7" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="AC57" s="7" t="s">
         <v>98</v>
@@ -10325,7 +10325,7 @@
         <v>7</v>
       </c>
       <c r="AK57" s="7" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="AL57" s="10">
         <f>IF(OR(A57="",COUNT(AF57:AJ57)&lt;5),"",ROUND(SUMPRODUCT(AF57:AJ57,Guia!$B$7:$F$7),1))</f>
@@ -10357,28 +10357,28 @@
     </row>
     <row r="58" spans="1:47" ht="32" customHeight="1">
       <c r="A58" s="7" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E58" s="7" t="s">
         <v>103</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="G58" s="7" t="s">
         <v>105</v>
       </c>
       <c r="H58" s="7" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="I58" s="7" t="s">
         <v>107</v>
@@ -10390,7 +10390,7 @@
         <v>109</v>
       </c>
       <c r="L58" s="7" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="M58" s="7" t="s">
         <v>111</v>
@@ -10417,28 +10417,28 @@
         <v>165</v>
       </c>
       <c r="U58" s="7" t="s">
+        <v>687</v>
+      </c>
+      <c r="V58" s="7" t="s">
+        <v>688</v>
+      </c>
+      <c r="W58" s="7" t="s">
+        <v>689</v>
+      </c>
+      <c r="X58" s="7" t="s">
         <v>690</v>
-      </c>
-      <c r="V58" s="7" t="s">
-        <v>691</v>
-      </c>
-      <c r="W58" s="7" t="s">
-        <v>692</v>
-      </c>
-      <c r="X58" s="7" t="s">
-        <v>693</v>
       </c>
       <c r="Y58" s="7" t="s">
         <v>118</v>
       </c>
       <c r="Z58" s="7" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="AA58" s="16">
         <v>46293</v>
       </c>
       <c r="AB58" s="7" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="AC58" s="7" t="s">
         <v>98</v>
@@ -10463,7 +10463,7 @@
         <v>7</v>
       </c>
       <c r="AK58" s="7" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="AL58" s="10">
         <f>IF(OR(A58="",COUNT(AF58:AJ58)&lt;5),"",ROUND(SUMPRODUCT(AF58:AJ58,Guia!$B$7:$F$7),1))</f>
@@ -10495,22 +10495,22 @@
     </row>
     <row r="59" spans="1:47" ht="32" customHeight="1">
       <c r="A59" s="7" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>103</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="G59" s="7" t="s">
         <v>105</v>
@@ -10528,7 +10528,7 @@
         <v>109</v>
       </c>
       <c r="L59" s="7" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="M59" s="7" t="s">
         <v>122</v>
@@ -10555,13 +10555,13 @@
         <v>165</v>
       </c>
       <c r="U59" s="7" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="V59" s="7" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="W59" s="7" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="X59" s="17" t="s">
         <v>204</v>
@@ -10570,13 +10570,13 @@
         <v>150</v>
       </c>
       <c r="Z59" s="7" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="AA59" s="16">
         <v>46293</v>
       </c>
       <c r="AB59" s="7" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="AC59" s="7" t="s">
         <v>98</v>
@@ -10601,7 +10601,7 @@
         <v>8</v>
       </c>
       <c r="AK59" s="7" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="AL59" s="10">
         <f>IF(OR(A59="",COUNT(AF59:AJ59)&lt;5),"",ROUND(SUMPRODUCT(AF59:AJ59,Guia!$B$7:$F$7),1))</f>
@@ -10633,22 +10633,22 @@
     </row>
     <row r="60" spans="1:47" ht="32" customHeight="1">
       <c r="A60" s="7" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="E60" s="7" t="s">
         <v>125</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="G60" s="7" t="s">
         <v>105</v>
@@ -10666,7 +10666,7 @@
         <v>109</v>
       </c>
       <c r="L60" s="7" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="M60" s="7" t="s">
         <v>122</v>
@@ -10693,13 +10693,13 @@
         <v>165</v>
       </c>
       <c r="U60" s="7" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="V60" s="7" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="W60" s="7" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="X60" s="17" t="s">
         <v>204</v>
@@ -10708,13 +10708,13 @@
         <v>150</v>
       </c>
       <c r="Z60" s="7" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="AA60" s="16">
         <v>46293</v>
       </c>
       <c r="AB60" s="7" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="AC60" s="7" t="s">
         <v>98</v>
@@ -10739,7 +10739,7 @@
         <v>8</v>
       </c>
       <c r="AK60" s="7" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="AL60" s="10">
         <f>IF(OR(A60="",COUNT(AF60:AJ60)&lt;5),"",ROUND(SUMPRODUCT(AF60:AJ60,Guia!$B$7:$F$7),1))</f>
@@ -10771,28 +10771,28 @@
     </row>
     <row r="61" spans="1:47" ht="32" customHeight="1">
       <c r="A61" s="7" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="E61" s="7" t="s">
         <v>103</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="G61" s="7" t="s">
         <v>105</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="I61" s="7" t="s">
         <v>107</v>
@@ -10804,7 +10804,7 @@
         <v>109</v>
       </c>
       <c r="L61" s="7" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="M61" s="7" t="s">
         <v>122</v>
@@ -10831,13 +10831,13 @@
         <v>165</v>
       </c>
       <c r="U61" s="7" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="V61" s="7" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="W61" s="7" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="X61" s="17" t="s">
         <v>204</v>
@@ -10846,13 +10846,13 @@
         <v>150</v>
       </c>
       <c r="Z61" s="7" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="AA61" s="16">
         <v>46293</v>
       </c>
       <c r="AB61" s="7" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="AC61" s="7" t="s">
         <v>98</v>
@@ -10877,7 +10877,7 @@
         <v>8</v>
       </c>
       <c r="AK61" s="7" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="AL61" s="10">
         <f>IF(OR(A61="",COUNT(AF61:AJ61)&lt;5),"",ROUND(SUMPRODUCT(AF61:AJ61,Guia!$B$7:$F$7),1))</f>
@@ -10909,22 +10909,22 @@
     </row>
     <row r="62" spans="1:47" ht="32" customHeight="1">
       <c r="A62" s="7" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="E62" s="7" t="s">
         <v>125</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="G62" s="7" t="s">
         <v>105</v>
@@ -10942,7 +10942,7 @@
         <v>109</v>
       </c>
       <c r="L62" s="7" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="M62" s="7" t="s">
         <v>122</v>
@@ -10969,26 +10969,26 @@
         <v>165</v>
       </c>
       <c r="U62" s="7" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="V62" s="7" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="W62" s="7" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="X62" s="7"/>
       <c r="Y62" s="7" t="s">
         <v>150</v>
       </c>
       <c r="Z62" s="7" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="AA62" s="16">
         <v>46293</v>
       </c>
       <c r="AB62" s="7" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="AC62" s="7" t="s">
         <v>98</v>
@@ -11013,7 +11013,7 @@
         <v>7</v>
       </c>
       <c r="AK62" s="7" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="AL62" s="10">
         <f>IF(OR(A62="",COUNT(AF62:AJ62)&lt;5),"",ROUND(SUMPRODUCT(AF62:AJ62,Guia!$B$7:$F$7),1))</f>
@@ -11045,22 +11045,22 @@
     </row>
     <row r="63" spans="1:47" ht="32" customHeight="1">
       <c r="A63" s="7" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="E63" s="7" t="s">
         <v>103</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="G63" s="7" t="s">
         <v>105</v>
@@ -11078,7 +11078,7 @@
         <v>109</v>
       </c>
       <c r="L63" s="7" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="M63" s="7" t="s">
         <v>122</v>
@@ -11105,26 +11105,26 @@
         <v>165</v>
       </c>
       <c r="U63" s="7" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="V63" s="7" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="W63" s="7" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="X63" s="7"/>
       <c r="Y63" s="7" t="s">
         <v>150</v>
       </c>
       <c r="Z63" s="7" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="AA63" s="16">
         <v>46293</v>
       </c>
       <c r="AB63" s="7" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="AC63" s="7" t="s">
         <v>98</v>
@@ -11149,7 +11149,7 @@
         <v>8</v>
       </c>
       <c r="AK63" s="7" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="AL63" s="10">
         <f>IF(OR(A63="",COUNT(AF63:AJ63)&lt;5),"",ROUND(SUMPRODUCT(AF63:AJ63,Guia!$B$7:$F$7),1))</f>
@@ -11181,16 +11181,16 @@
     </row>
     <row r="64" spans="1:47" ht="32" customHeight="1">
       <c r="A64" s="7" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>103</v>
@@ -11214,7 +11214,7 @@
         <v>190</v>
       </c>
       <c r="L64" s="7" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="M64" s="7" t="s">
         <v>112</v>
@@ -11241,28 +11241,28 @@
         <v>165</v>
       </c>
       <c r="U64" s="7" t="s">
+        <v>745</v>
+      </c>
+      <c r="V64" s="7" t="s">
+        <v>746</v>
+      </c>
+      <c r="W64" s="7" t="s">
+        <v>747</v>
+      </c>
+      <c r="X64" s="7" t="s">
         <v>748</v>
-      </c>
-      <c r="V64" s="7" t="s">
-        <v>749</v>
-      </c>
-      <c r="W64" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="X64" s="7" t="s">
-        <v>751</v>
       </c>
       <c r="Y64" s="7" t="s">
         <v>118</v>
       </c>
       <c r="Z64" s="7" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="AA64" s="16">
         <v>46293</v>
       </c>
       <c r="AB64" s="7" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="AC64" s="7" t="s">
         <v>98</v>
@@ -11287,7 +11287,7 @@
         <v>6</v>
       </c>
       <c r="AK64" s="7" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="AL64" s="10">
         <f>IF(OR(A64="",COUNT(AF64:AJ64)&lt;5),"",ROUND(SUMPRODUCT(AF64:AJ64,Guia!$B$7:$F$7),1))</f>
@@ -11319,16 +11319,16 @@
     </row>
     <row r="65" spans="1:47" ht="32" customHeight="1">
       <c r="A65" s="7" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="E65" s="7" t="s">
         <v>125</v>
@@ -11377,28 +11377,28 @@
         <v>165</v>
       </c>
       <c r="U65" s="7" t="s">
+        <v>754</v>
+      </c>
+      <c r="V65" s="7" t="s">
+        <v>755</v>
+      </c>
+      <c r="W65" s="7" t="s">
+        <v>756</v>
+      </c>
+      <c r="X65" s="7" t="s">
         <v>757</v>
-      </c>
-      <c r="V65" s="7" t="s">
-        <v>758</v>
-      </c>
-      <c r="W65" s="7" t="s">
-        <v>759</v>
-      </c>
-      <c r="X65" s="7" t="s">
-        <v>760</v>
       </c>
       <c r="Y65" s="7" t="s">
         <v>118</v>
       </c>
       <c r="Z65" s="7" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="AA65" s="16">
         <v>46293</v>
       </c>
       <c r="AB65" s="7" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="AC65" s="7" t="s">
         <v>98</v>
@@ -11423,7 +11423,7 @@
         <v>6</v>
       </c>
       <c r="AK65" s="7" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="AL65" s="10">
         <f>IF(OR(A65="",COUNT(AF65:AJ65)&lt;5),"",ROUND(SUMPRODUCT(AF65:AJ65,Guia!$B$7:$F$7),1))</f>
@@ -11455,16 +11455,16 @@
     </row>
     <row r="66" spans="1:47" ht="32" customHeight="1">
       <c r="A66" s="7" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="E66" s="7" t="s">
         <v>103</v>
@@ -11488,7 +11488,7 @@
         <v>190</v>
       </c>
       <c r="L66" s="7" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="M66" s="7" t="s">
         <v>112</v>
@@ -11515,26 +11515,26 @@
         <v>122</v>
       </c>
       <c r="U66" s="7" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="V66" s="7" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="W66" s="7" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="X66" s="7"/>
       <c r="Y66" s="7" t="s">
         <v>150</v>
       </c>
       <c r="Z66" s="7" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="AA66" s="16">
         <v>46293</v>
       </c>
       <c r="AB66" s="7" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="AC66" s="7" t="s">
         <v>98</v>
@@ -11559,7 +11559,7 @@
         <v>7</v>
       </c>
       <c r="AK66" s="7" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="AL66" s="10">
         <f>IF(OR(A66="",COUNT(AF66:AJ66)&lt;5),"",ROUND(SUMPRODUCT(AF66:AJ66,Guia!$B$7:$F$7),1))</f>

--- a/_proyecto/Registro_Negocios.xlsx
+++ b/_proyecto/Registro_Negocios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecnalia365-my.sharepoint.com/personal/inigo_arana_tecnalia_com/Documents/Escritorio/Personal/Cursor_Web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4744" documentId="11_180DE2EEB12A76AE30F8224BFABDEE52E13E727D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2797C0C-6C48-4DB2-9587-481A429BD38D}"/>
+  <xr:revisionPtr revIDLastSave="4887" documentId="11_180DE2EEB12A76AE30F8224BFABDEE52E13E727D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AAA4F24A-6574-43D7-9F80-BA1FF59353B8}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2320" uniqueCount="776">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2322" uniqueCount="778">
   <si>
     <t>Registro de negocios</t>
   </si>
@@ -810,9 +810,6 @@
     <t>Seleccionado</t>
   </si>
   <si>
-    <t>Mejor nota (6,8); encaje claro; web propia + carta vs Eatbu.</t>
-  </si>
-  <si>
     <t>En curso</t>
   </si>
   <si>
@@ -822,9 +819,6 @@
     <t>Operativa muy tradicional; urgencia digital menor que alternativas encaje claro.</t>
   </si>
   <si>
-    <t>Dominio barmugi.com inactivo/spam; web mínima en espera tras activo.</t>
-  </si>
-  <si>
     <t>expedientes/0001_Indusi</t>
   </si>
   <si>
@@ -891,9 +885,6 @@
     <t>6 Valoración</t>
   </si>
   <si>
-    <t>Post demo/comercial: web propia suma SEO, homónimos y carta/horario vs Eatbu; demos A/B e infografía v3 validadas. Techo por Eatbu existente, sin reserva en v1, conversión incierta. seguir_7_mensajero.</t>
-  </si>
-  <si>
     <t>indh016</t>
   </si>
   <si>
@@ -2349,19 +2340,34 @@
     <t>Brief 02 completado; cola Puntuación 8,3; activo pipeline 3-7.</t>
   </si>
   <si>
-    <t>Post demo+comercial: dolor IONOS/PDF/móvil confirmado; demo A encaja mediodía Indautxu. No 9: sin IG, reserva telefónica, horario/carta por validar; conversión incierta. Prioridad campaña; seguir con mensajero (email/visita).</t>
+    <t>laciadelron.com (hijack/spam); Instagram @la_compania_del_ron; Facebook Laciadelron22; Google 643802270; tel. hist. 944024844</t>
+  </si>
+  <si>
+    <t>Dominio histórico con contenido ajeno; sin carta propia; teléfonos discordantes en fuentes.</t>
+  </si>
+  <si>
+    <t>https://laciadelron.com/ | https://www.instagram.com/la_compania_del_ron/ | expedientes/0050_CompaniaDelRon/04-alcance-aceptado.json</t>
+  </si>
+  <si>
+    <t>Rehacer 5 Comercial v2 (2026-09-29); pendiente /6-valoracion-impacto.</t>
+  </si>
+  <si>
+    <t>Rehacer 5 Comercial SKILL v2 (2026-09-30); pendiente /6-valoracion-impacto.</t>
+  </si>
+  <si>
+    <t>Rehacer pack demos v4 skill principios conversión; demos/ A+B+C</t>
+  </si>
+  <si>
+    <t>Cola /2-webscraper 2026-09-30 (7,5); brief indh010 Mugi completado</t>
+  </si>
+  <si>
+    <t>Pipeline 0047 2026-09-30</t>
+  </si>
+  <si>
+    <t>Post demo+comercial: vitrina honesta vs barmugi.com, horario/carta/tel creíbles; demos pulidas (feedback reciente). No 9: dueño sin validar, reserva telefónica, fotos stock. seguir_7_mensajero.</t>
   </si>
   <si>
     <t>Completado</t>
-  </si>
-  <si>
-    <t>laciadelron.com (hijack/spam); Instagram @la_compania_del_ron; Facebook Laciadelron22; Google 643802270; tel. hist. 944024844</t>
-  </si>
-  <si>
-    <t>Dominio histórico con contenido ajeno; sin carta propia; teléfonos discordantes en fuentes.</t>
-  </si>
-  <si>
-    <t>https://laciadelron.com/ | https://www.instagram.com/la_compania_del_ron/ | expedientes/0050_CompaniaDelRon/04-alcance-aceptado.json</t>
   </si>
 </sst>
 </file>
@@ -3088,7 +3094,7 @@
       </c>
       <c r="H4" s="1">
         <f>COUNTIFS(AC7:AC206,"Seleccionado",A7:A206,"&lt;&gt;")</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1" t="s">
@@ -3298,28 +3304,28 @@
         <v>42</v>
       </c>
       <c r="AM6" s="5" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AN6" s="5" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AO6" s="4" t="s">
         <v>43</v>
       </c>
       <c r="AP6" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="AQ6" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="AR6" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="AQ6" s="4" t="s">
+      <c r="AS6" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="AR6" s="4" t="s">
+      <c r="AT6" s="4" t="s">
         <v>282</v>
-      </c>
-      <c r="AS6" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="AT6" s="4" t="s">
-        <v>284</v>
       </c>
       <c r="AU6" s="4" t="s">
         <v>44</v>
@@ -3408,7 +3414,7 @@
         <v>46292</v>
       </c>
       <c r="AB7" s="7" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AC7" s="7" t="s">
         <v>98</v>
@@ -3546,14 +3552,14 @@
         <v>46292</v>
       </c>
       <c r="AB8" s="7" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="AC8" s="7" t="s">
-        <v>98</v>
+        <v>257</v>
       </c>
       <c r="AD8" s="7"/>
       <c r="AE8" s="7" t="s">
-        <v>120</v>
+        <v>258</v>
       </c>
       <c r="AF8" s="9">
         <v>6</v>
@@ -3583,16 +3589,16 @@
         <v>122</v>
       </c>
       <c r="AP8" s="7" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="AQ8" s="7" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="AR8" s="7" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="AS8" s="7" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="AT8" s="7" t="s">
         <v>97</v>
@@ -3684,7 +3690,7 @@
         <v>46292</v>
       </c>
       <c r="AB9" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="AC9" s="7" t="s">
         <v>98</v>
@@ -3822,7 +3828,7 @@
         <v>46292</v>
       </c>
       <c r="AB10" s="7" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="AC10" s="7" t="s">
         <v>98</v>
@@ -3958,13 +3964,13 @@
         <v>46293</v>
       </c>
       <c r="AB11" s="7" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AC11" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="AD11" s="7" t="s">
         <v>260</v>
-      </c>
-      <c r="AD11" s="7" t="s">
-        <v>261</v>
       </c>
       <c r="AE11" s="7" t="s">
         <v>120</v>
@@ -3985,7 +3991,7 @@
         <v>7</v>
       </c>
       <c r="AK11" s="7" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="AL11" s="10">
         <f>IF(OR(A11="",COUNT(AF11:AJ11)&lt;5),"",ROUND(SUMPRODUCT(AF11:AJ11,Guia!$B$7:$F$7),1))</f>
@@ -4098,7 +4104,7 @@
         <v>46292</v>
       </c>
       <c r="AB12" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AC12" s="7" t="s">
         <v>98</v>
@@ -4236,7 +4242,7 @@
         <v>46292</v>
       </c>
       <c r="AB13" s="7" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AC13" s="7" t="s">
         <v>98</v>
@@ -4371,19 +4377,19 @@
         <v>196</v>
       </c>
       <c r="AA14" s="16">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="AB14" s="7" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AC14" s="7" t="s">
         <v>257</v>
       </c>
       <c r="AD14" s="7" t="s">
+        <v>773</v>
+      </c>
+      <c r="AE14" s="7" t="s">
         <v>258</v>
-      </c>
-      <c r="AE14" s="7" t="s">
-        <v>259</v>
       </c>
       <c r="AF14" s="9">
         <v>7</v>
@@ -4401,17 +4407,15 @@
         <v>8</v>
       </c>
       <c r="AK14" s="7" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="AL14" s="10">
         <f>IF(OR(A14="",COUNT(AF14:AJ14)&lt;5),"",ROUND(SUMPRODUCT(AF14:AJ14,Guia!$B$7:$F$7),1))</f>
         <v>7.3</v>
       </c>
-      <c r="AM14" s="10">
-        <v>7</v>
-      </c>
+      <c r="AM14" s="10"/>
       <c r="AN14" s="10" t="s">
-        <v>285</v>
+        <v>771</v>
       </c>
       <c r="AO14" s="7" t="s">
         <v>122</v>
@@ -4429,7 +4433,7 @@
         <v>122</v>
       </c>
       <c r="AT14" s="7" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="AU14" s="7" t="s">
         <v>97</v>
@@ -4518,7 +4522,7 @@
         <v>46292</v>
       </c>
       <c r="AB15" s="7" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AC15" s="7" t="s">
         <v>98</v>
@@ -4654,16 +4658,16 @@
         <v>46293</v>
       </c>
       <c r="AB16" s="7" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AC16" s="7" t="s">
         <v>257</v>
       </c>
       <c r="AD16" s="7" t="s">
-        <v>262</v>
+        <v>774</v>
       </c>
       <c r="AE16" s="7" t="s">
-        <v>120</v>
+        <v>777</v>
       </c>
       <c r="AF16" s="9">
         <v>7</v>
@@ -4681,34 +4685,38 @@
         <v>7</v>
       </c>
       <c r="AK16" s="7" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="AL16" s="10">
         <f>IF(OR(A16="",COUNT(AF16:AJ16)&lt;5),"",ROUND(SUMPRODUCT(AF16:AJ16,Guia!$B$7:$F$7),1))</f>
         <v>7.5</v>
       </c>
-      <c r="AM16" s="10"/>
-      <c r="AN16" s="10"/>
+      <c r="AM16" s="10">
+        <v>8</v>
+      </c>
+      <c r="AN16" s="10" t="s">
+        <v>776</v>
+      </c>
       <c r="AO16" s="7" t="s">
         <v>122</v>
       </c>
       <c r="AP16" s="7" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="AQ16" s="7" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="AR16" s="7" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="AS16" s="7" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="AT16" s="7" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="AU16" s="7" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:47" ht="32" customHeight="1">
@@ -4777,7 +4785,7 @@
         <v>232</v>
       </c>
       <c r="W17" s="7" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="X17" s="7" t="s">
         <v>233</v>
@@ -4792,7 +4800,7 @@
         <v>46293</v>
       </c>
       <c r="AB17" s="7" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AC17" s="7" t="s">
         <v>98</v>
@@ -4817,7 +4825,7 @@
         <v>7</v>
       </c>
       <c r="AK17" s="7" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="AL17" s="10">
         <f>IF(OR(A17="",COUNT(AF17:AJ17)&lt;5),"",ROUND(SUMPRODUCT(AF17:AJ17,Guia!$B$7:$F$7),1))</f>
@@ -4928,7 +4936,7 @@
         <v>46293</v>
       </c>
       <c r="AB18" s="7" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="AC18" s="7" t="s">
         <v>98</v>
@@ -4953,7 +4961,7 @@
         <v>7</v>
       </c>
       <c r="AK18" s="7" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="AL18" s="10">
         <f>IF(OR(A18="",COUNT(AF18:AJ18)&lt;5),"",ROUND(SUMPRODUCT(AF18:AJ18,Guia!$B$7:$F$7),1))</f>
@@ -5064,7 +5072,7 @@
         <v>46293</v>
       </c>
       <c r="AB19" s="7" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AC19" s="7" t="s">
         <v>98</v>
@@ -5089,7 +5097,7 @@
         <v>7</v>
       </c>
       <c r="AK19" s="7" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="AL19" s="10">
         <f>IF(OR(A19="",COUNT(AF19:AJ19)&lt;5),"",ROUND(SUMPRODUCT(AF19:AJ19,Guia!$B$7:$F$7),1))</f>
@@ -5202,7 +5210,7 @@
         <v>46292</v>
       </c>
       <c r="AB20" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AC20" s="7" t="s">
         <v>98</v>
@@ -5338,7 +5346,7 @@
         <v>46292</v>
       </c>
       <c r="AB21" s="7" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AC21" s="7" t="s">
         <v>98</v>
@@ -5395,22 +5403,22 @@
     </row>
     <row r="22" spans="1:47" ht="32" customHeight="1">
       <c r="A22" s="7" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>103</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="G22" s="7" t="s">
         <v>105</v>
@@ -5428,7 +5436,7 @@
         <v>109</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="M22" s="7" t="s">
         <v>122</v>
@@ -5455,28 +5463,28 @@
         <v>122</v>
       </c>
       <c r="U22" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="V22" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="W22" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="X22" s="7" t="s">
         <v>309</v>
-      </c>
-      <c r="V22" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="W22" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="X22" s="7" t="s">
-        <v>312</v>
       </c>
       <c r="Y22" s="7" t="s">
         <v>118</v>
       </c>
       <c r="Z22" s="7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AA22" s="16">
         <v>46293</v>
       </c>
       <c r="AB22" s="7" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="AC22" s="7" t="s">
         <v>98</v>
@@ -5501,7 +5509,7 @@
         <v>8</v>
       </c>
       <c r="AK22" s="7" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="AL22" s="10">
         <f>IF(OR(A22="",COUNT(AF22:AJ22)&lt;5),"",ROUND(SUMPRODUCT(AF22:AJ22,Guia!$B$7:$F$7),1))</f>
@@ -5533,22 +5541,22 @@
     </row>
     <row r="23" spans="1:47" ht="32" customHeight="1">
       <c r="A23" s="7" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>103</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="G23" s="7" t="s">
         <v>105</v>
@@ -5591,28 +5599,28 @@
         <v>165</v>
       </c>
       <c r="U23" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="V23" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="W23" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="X23" s="7" t="s">
         <v>315</v>
-      </c>
-      <c r="V23" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="W23" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="X23" s="7" t="s">
-        <v>318</v>
       </c>
       <c r="Y23" s="7" t="s">
         <v>162</v>
       </c>
       <c r="Z23" s="7" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AA23" s="16">
         <v>46293</v>
       </c>
       <c r="AB23" s="7" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="AC23" s="7" t="s">
         <v>98</v>
@@ -5637,7 +5645,7 @@
         <v>7</v>
       </c>
       <c r="AK23" s="7" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="AL23" s="10">
         <f>IF(OR(A23="",COUNT(AF23:AJ23)&lt;5),"",ROUND(SUMPRODUCT(AF23:AJ23,Guia!$B$7:$F$7),1))</f>
@@ -5669,22 +5677,22 @@
     </row>
     <row r="24" spans="1:47" ht="32" customHeight="1">
       <c r="A24" s="7" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G24" s="7" t="s">
         <v>105</v>
@@ -5702,7 +5710,7 @@
         <v>109</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="M24" s="7" t="s">
         <v>111</v>
@@ -5729,28 +5737,28 @@
         <v>165</v>
       </c>
       <c r="U24" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="V24" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="W24" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="X24" s="7" t="s">
         <v>321</v>
-      </c>
-      <c r="V24" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="W24" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="X24" s="7" t="s">
-        <v>324</v>
       </c>
       <c r="Y24" s="7" t="s">
         <v>118</v>
       </c>
       <c r="Z24" s="7" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="AA24" s="16">
         <v>46293</v>
       </c>
       <c r="AB24" s="7" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="AC24" s="7" t="s">
         <v>98</v>
@@ -5775,7 +5783,7 @@
         <v>8</v>
       </c>
       <c r="AK24" s="7" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="AL24" s="10">
         <f>IF(OR(A24="",COUNT(AF24:AJ24)&lt;5),"",ROUND(SUMPRODUCT(AF24:AJ24,Guia!$B$7:$F$7),1))</f>
@@ -5807,22 +5815,22 @@
     </row>
     <row r="25" spans="1:47" ht="32" customHeight="1">
       <c r="A25" s="7" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>125</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G25" s="7" t="s">
         <v>105</v>
@@ -5840,7 +5848,7 @@
         <v>109</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="M25" s="7" t="s">
         <v>111</v>
@@ -5867,28 +5875,28 @@
         <v>122</v>
       </c>
       <c r="U25" s="7" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="V25" s="7" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="W25" s="7" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="X25" s="7" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="Y25" s="7" t="s">
         <v>118</v>
       </c>
       <c r="Z25" s="7" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="AA25" s="16">
         <v>46293</v>
       </c>
       <c r="AB25" s="7" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="AC25" s="7" t="s">
         <v>98</v>
@@ -5913,7 +5921,7 @@
         <v>6</v>
       </c>
       <c r="AK25" s="7" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="AL25" s="10">
         <f>IF(OR(A25="",COUNT(AF25:AJ25)&lt;5),"",ROUND(SUMPRODUCT(AF25:AJ25,Guia!$B$7:$F$7),1))</f>
@@ -5945,22 +5953,22 @@
     </row>
     <row r="26" spans="1:47" ht="32" customHeight="1">
       <c r="A26" s="7" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>103</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G26" s="7" t="s">
         <v>105</v>
@@ -5978,7 +5986,7 @@
         <v>109</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="M26" s="7" t="s">
         <v>122</v>
@@ -6005,28 +6013,28 @@
         <v>165</v>
       </c>
       <c r="U26" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="V26" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="W26" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="X26" s="7" t="s">
         <v>331</v>
-      </c>
-      <c r="V26" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="W26" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="X26" s="7" t="s">
-        <v>334</v>
       </c>
       <c r="Y26" s="7" t="s">
         <v>118</v>
       </c>
       <c r="Z26" s="7" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="AA26" s="16">
         <v>46293</v>
       </c>
       <c r="AB26" s="7" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="AC26" s="7" t="s">
         <v>98</v>
@@ -6051,7 +6059,7 @@
         <v>7</v>
       </c>
       <c r="AK26" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="AL26" s="10">
         <f>IF(OR(A26="",COUNT(AF26:AJ26)&lt;5),"",ROUND(SUMPRODUCT(AF26:AJ26,Guia!$B$7:$F$7),1))</f>
@@ -6083,22 +6091,22 @@
     </row>
     <row r="27" spans="1:47" ht="32" customHeight="1">
       <c r="A27" s="7" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>125</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="G27" s="7" t="s">
         <v>105</v>
@@ -6116,7 +6124,7 @@
         <v>109</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="M27" s="7" t="s">
         <v>122</v>
@@ -6143,13 +6151,13 @@
         <v>122</v>
       </c>
       <c r="U27" s="7" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="V27" s="7" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="W27" s="7" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="X27" s="7" t="s">
         <v>140</v>
@@ -6158,13 +6166,13 @@
         <v>150</v>
       </c>
       <c r="Z27" s="7" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="AA27" s="16">
         <v>46293</v>
       </c>
       <c r="AB27" s="7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="AC27" s="7" t="s">
         <v>98</v>
@@ -6189,7 +6197,7 @@
         <v>8</v>
       </c>
       <c r="AK27" s="7" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="AL27" s="10">
         <f>IF(OR(A27="",COUNT(AF27:AJ27)&lt;5),"",ROUND(SUMPRODUCT(AF27:AJ27,Guia!$B$7:$F$7),1))</f>
@@ -6221,22 +6229,22 @@
     </row>
     <row r="28" spans="1:47" ht="32" customHeight="1">
       <c r="A28" s="7" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>125</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="G28" s="7" t="s">
         <v>105</v>
@@ -6279,37 +6287,37 @@
         <v>122</v>
       </c>
       <c r="U28" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="V28" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="W28" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="X28" s="7" t="s">
         <v>360</v>
-      </c>
-      <c r="V28" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="W28" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="X28" s="7" t="s">
-        <v>363</v>
       </c>
       <c r="Y28" s="7" t="s">
         <v>162</v>
       </c>
       <c r="Z28" s="7" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="AA28" s="16">
         <v>46293</v>
       </c>
       <c r="AB28" s="7" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="AC28" s="7" t="s">
         <v>257</v>
       </c>
       <c r="AD28" s="7" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AE28" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AF28" s="9">
         <v>7</v>
@@ -6327,7 +6335,7 @@
         <v>7</v>
       </c>
       <c r="AK28" s="7" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="AL28" s="10">
         <f>IF(OR(A28="",COUNT(AF28:AJ28)&lt;5),"",ROUND(SUMPRODUCT(AF28:AJ28,Guia!$B$7:$F$7),1))</f>
@@ -6359,22 +6367,22 @@
     </row>
     <row r="29" spans="1:47" ht="32" customHeight="1">
       <c r="A29" s="7" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>125</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="G29" s="7" t="s">
         <v>105</v>
@@ -6392,7 +6400,7 @@
         <v>109</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="M29" s="7" t="s">
         <v>111</v>
@@ -6419,28 +6427,28 @@
         <v>122</v>
       </c>
       <c r="U29" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="V29" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="W29" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="X29" s="7" t="s">
         <v>366</v>
-      </c>
-      <c r="V29" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="W29" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="X29" s="7" t="s">
-        <v>369</v>
       </c>
       <c r="Y29" s="7" t="s">
         <v>118</v>
       </c>
       <c r="Z29" s="7" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="AA29" s="16">
         <v>46293</v>
       </c>
       <c r="AB29" s="7" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="AC29" s="7" t="s">
         <v>98</v>
@@ -6465,7 +6473,7 @@
         <v>8</v>
       </c>
       <c r="AK29" s="7" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="AL29" s="10">
         <f>IF(OR(A29="",COUNT(AF29:AJ29)&lt;5),"",ROUND(SUMPRODUCT(AF29:AJ29,Guia!$B$7:$F$7),1))</f>
@@ -6497,22 +6505,22 @@
     </row>
     <row r="30" spans="1:47" ht="32" customHeight="1">
       <c r="A30" s="7" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>103</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="G30" s="7" t="s">
         <v>105</v>
@@ -6530,7 +6538,7 @@
         <v>109</v>
       </c>
       <c r="L30" s="7" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="M30" s="7" t="s">
         <v>111</v>
@@ -6557,28 +6565,28 @@
         <v>122</v>
       </c>
       <c r="U30" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="V30" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="W30" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="X30" s="7" t="s">
         <v>373</v>
-      </c>
-      <c r="V30" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="W30" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="X30" s="7" t="s">
-        <v>376</v>
       </c>
       <c r="Y30" s="7" t="s">
         <v>118</v>
       </c>
       <c r="Z30" s="7" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="AA30" s="16">
         <v>46293</v>
       </c>
       <c r="AB30" s="7" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="AC30" s="7" t="s">
         <v>98</v>
@@ -6603,7 +6611,7 @@
         <v>8</v>
       </c>
       <c r="AK30" s="7" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="AL30" s="10">
         <f>IF(OR(A30="",COUNT(AF30:AJ30)&lt;5),"",ROUND(SUMPRODUCT(AF30:AJ30,Guia!$B$7:$F$7),1))</f>
@@ -6635,22 +6643,22 @@
     </row>
     <row r="31" spans="1:47" ht="32" customHeight="1">
       <c r="A31" s="7" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>125</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="G31" s="7" t="s">
         <v>105</v>
@@ -6693,28 +6701,28 @@
         <v>122</v>
       </c>
       <c r="U31" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="V31" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="W31" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="X31" s="7" t="s">
         <v>379</v>
-      </c>
-      <c r="V31" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="W31" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="X31" s="7" t="s">
-        <v>382</v>
       </c>
       <c r="Y31" s="7" t="s">
         <v>162</v>
       </c>
       <c r="Z31" s="7" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="AA31" s="16">
         <v>46293</v>
       </c>
       <c r="AB31" s="7" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="AC31" s="7" t="s">
         <v>98</v>
@@ -6739,7 +6747,7 @@
         <v>7</v>
       </c>
       <c r="AK31" s="7" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="AL31" s="10">
         <f>IF(OR(A31="",COUNT(AF31:AJ31)&lt;5),"",ROUND(SUMPRODUCT(AF31:AJ31,Guia!$B$7:$F$7),1))</f>
@@ -6771,16 +6779,16 @@
     </row>
     <row r="32" spans="1:47" ht="32" customHeight="1">
       <c r="A32" s="7" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>125</v>
@@ -6829,28 +6837,28 @@
         <v>122</v>
       </c>
       <c r="U32" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="V32" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="W32" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="X32" s="7" t="s">
         <v>404</v>
-      </c>
-      <c r="V32" s="7" t="s">
-        <v>405</v>
-      </c>
-      <c r="W32" s="7" t="s">
-        <v>406</v>
-      </c>
-      <c r="X32" s="7" t="s">
-        <v>407</v>
       </c>
       <c r="Y32" s="7" t="s">
         <v>118</v>
       </c>
       <c r="Z32" s="7" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="AA32" s="16">
         <v>46293</v>
       </c>
       <c r="AB32" s="7" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="AC32" s="7" t="s">
         <v>98</v>
@@ -6875,7 +6883,7 @@
         <v>7</v>
       </c>
       <c r="AK32" s="7" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="AL32" s="10">
         <f>IF(OR(A32="",COUNT(AF32:AJ32)&lt;5),"",ROUND(SUMPRODUCT(AF32:AJ32,Guia!$B$7:$F$7),1))</f>
@@ -6907,22 +6915,22 @@
     </row>
     <row r="33" spans="1:47" ht="32" customHeight="1">
       <c r="A33" s="7" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G33" s="7" t="s">
         <v>105</v>
@@ -6940,7 +6948,7 @@
         <v>109</v>
       </c>
       <c r="L33" s="7" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M33" s="7" t="s">
         <v>122</v>
@@ -6967,28 +6975,28 @@
         <v>165</v>
       </c>
       <c r="U33" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="V33" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="W33" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="X33" s="7" t="s">
         <v>410</v>
-      </c>
-      <c r="V33" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="W33" s="7" t="s">
-        <v>412</v>
-      </c>
-      <c r="X33" s="7" t="s">
-        <v>413</v>
       </c>
       <c r="Y33" s="7" t="s">
         <v>118</v>
       </c>
       <c r="Z33" s="7" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="AA33" s="16">
         <v>46293</v>
       </c>
       <c r="AB33" s="7" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="AC33" s="7" t="s">
         <v>98</v>
@@ -7013,7 +7021,7 @@
         <v>7</v>
       </c>
       <c r="AK33" s="7" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="AL33" s="10">
         <f>IF(OR(A33="",COUNT(AF33:AJ33)&lt;5),"",ROUND(SUMPRODUCT(AF33:AJ33,Guia!$B$7:$F$7),1))</f>
@@ -7045,22 +7053,22 @@
     </row>
     <row r="34" spans="1:47" ht="32" customHeight="1">
       <c r="A34" s="7" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>103</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="G34" s="7" t="s">
         <v>105</v>
@@ -7078,7 +7086,7 @@
         <v>109</v>
       </c>
       <c r="L34" s="7" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="M34" s="7" t="s">
         <v>111</v>
@@ -7105,28 +7113,28 @@
         <v>122</v>
       </c>
       <c r="U34" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="V34" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="W34" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="X34" s="7" t="s">
         <v>417</v>
-      </c>
-      <c r="V34" s="7" t="s">
-        <v>418</v>
-      </c>
-      <c r="W34" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="X34" s="7" t="s">
-        <v>420</v>
       </c>
       <c r="Y34" s="7" t="s">
         <v>118</v>
       </c>
       <c r="Z34" s="7" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="AA34" s="16">
         <v>46293</v>
       </c>
       <c r="AB34" s="7" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AC34" s="7" t="s">
         <v>98</v>
@@ -7151,7 +7159,7 @@
         <v>8</v>
       </c>
       <c r="AK34" s="7" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="AL34" s="10">
         <f>IF(OR(A34="",COUNT(AF34:AJ34)&lt;5),"",ROUND(SUMPRODUCT(AF34:AJ34,Guia!$B$7:$F$7),1))</f>
@@ -7183,22 +7191,22 @@
     </row>
     <row r="35" spans="1:47" ht="32" customHeight="1">
       <c r="A35" s="7" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>125</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="G35" s="7" t="s">
         <v>105</v>
@@ -7216,7 +7224,7 @@
         <v>236</v>
       </c>
       <c r="L35" s="7" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="M35" s="7" t="s">
         <v>111</v>
@@ -7243,28 +7251,28 @@
         <v>122</v>
       </c>
       <c r="U35" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="V35" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="W35" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="X35" s="7" t="s">
         <v>424</v>
-      </c>
-      <c r="V35" s="7" t="s">
-        <v>425</v>
-      </c>
-      <c r="W35" s="7" t="s">
-        <v>426</v>
-      </c>
-      <c r="X35" s="7" t="s">
-        <v>427</v>
       </c>
       <c r="Y35" s="7" t="s">
         <v>118</v>
       </c>
       <c r="Z35" s="7" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="AA35" s="16">
         <v>46293</v>
       </c>
       <c r="AB35" s="7" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AC35" s="7" t="s">
         <v>98</v>
@@ -7289,7 +7297,7 @@
         <v>7</v>
       </c>
       <c r="AK35" s="7" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AL35" s="10">
         <f>IF(OR(A35="",COUNT(AF35:AJ35)&lt;5),"",ROUND(SUMPRODUCT(AF35:AJ35,Guia!$B$7:$F$7),1))</f>
@@ -7321,22 +7329,22 @@
     </row>
     <row r="36" spans="1:47" ht="32" customHeight="1">
       <c r="A36" s="7" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>125</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="G36" s="7" t="s">
         <v>105</v>
@@ -7379,37 +7387,37 @@
         <v>165</v>
       </c>
       <c r="U36" s="7" t="s">
+        <v>530</v>
+      </c>
+      <c r="V36" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="W36" s="7" t="s">
         <v>533</v>
       </c>
-      <c r="V36" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="W36" s="7" t="s">
-        <v>536</v>
-      </c>
       <c r="X36" s="7" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="Y36" s="7" t="s">
         <v>162</v>
       </c>
       <c r="Z36" s="7" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="AA36" s="16">
         <v>46293</v>
       </c>
       <c r="AB36" s="7" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="AC36" s="7" t="s">
         <v>257</v>
       </c>
       <c r="AD36" s="7" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="AE36" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AF36" s="9">
         <v>7</v>
@@ -7427,7 +7435,7 @@
         <v>6</v>
       </c>
       <c r="AK36" s="7" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="AL36" s="10">
         <f>IF(OR(A36="",COUNT(AF36:AJ36)&lt;5),"",ROUND(SUMPRODUCT(AF36:AJ36,Guia!$B$7:$F$7),1))</f>
@@ -7459,22 +7467,22 @@
     </row>
     <row r="37" spans="1:47" ht="32" customHeight="1">
       <c r="A37" s="7" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>125</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="G37" s="7" t="s">
         <v>105</v>
@@ -7517,28 +7525,28 @@
         <v>122</v>
       </c>
       <c r="U37" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="V37" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="W37" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="X37" s="7" t="s">
         <v>454</v>
-      </c>
-      <c r="V37" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="W37" s="7" t="s">
-        <v>456</v>
-      </c>
-      <c r="X37" s="7" t="s">
-        <v>457</v>
       </c>
       <c r="Y37" s="7" t="s">
         <v>118</v>
       </c>
       <c r="Z37" s="7" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="AA37" s="16">
         <v>46293</v>
       </c>
       <c r="AB37" s="7" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="AC37" s="7" t="s">
         <v>98</v>
@@ -7563,7 +7571,7 @@
         <v>7</v>
       </c>
       <c r="AK37" s="7" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="AL37" s="10">
         <f>IF(OR(A37="",COUNT(AF37:AJ37)&lt;5),"",ROUND(SUMPRODUCT(AF37:AJ37,Guia!$B$7:$F$7),1))</f>
@@ -7595,22 +7603,22 @@
     </row>
     <row r="38" spans="1:47" ht="32" customHeight="1">
       <c r="A38" s="7" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E38" s="7" t="s">
         <v>103</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="G38" s="7" t="s">
         <v>105</v>
@@ -7628,7 +7636,7 @@
         <v>109</v>
       </c>
       <c r="L38" s="7" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="M38" s="7" t="s">
         <v>122</v>
@@ -7655,28 +7663,28 @@
         <v>122</v>
       </c>
       <c r="U38" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="V38" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="W38" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="X38" s="7" t="s">
         <v>460</v>
-      </c>
-      <c r="V38" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="W38" s="7" t="s">
-        <v>462</v>
-      </c>
-      <c r="X38" s="7" t="s">
-        <v>463</v>
       </c>
       <c r="Y38" s="7" t="s">
         <v>118</v>
       </c>
       <c r="Z38" s="7" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AA38" s="16">
         <v>46293</v>
       </c>
       <c r="AB38" s="7" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="AC38" s="7" t="s">
         <v>98</v>
@@ -7701,7 +7709,7 @@
         <v>8</v>
       </c>
       <c r="AK38" s="7" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="AL38" s="10">
         <f>IF(OR(A38="",COUNT(AF38:AJ38)&lt;5),"",ROUND(SUMPRODUCT(AF38:AJ38,Guia!$B$7:$F$7),1))</f>
@@ -7733,28 +7741,28 @@
     </row>
     <row r="39" spans="1:47" ht="32" customHeight="1">
       <c r="A39" s="7" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E39" s="7" t="s">
         <v>103</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="G39" s="7" t="s">
         <v>105</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="I39" s="7" t="s">
         <v>107</v>
@@ -7766,7 +7774,7 @@
         <v>109</v>
       </c>
       <c r="L39" s="7" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="M39" s="7" t="s">
         <v>122</v>
@@ -7793,13 +7801,13 @@
         <v>122</v>
       </c>
       <c r="U39" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="V39" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="W39" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="X39" s="17" t="s">
         <v>204</v>
@@ -7808,13 +7816,13 @@
         <v>150</v>
       </c>
       <c r="Z39" s="7" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="AA39" s="16">
         <v>46293</v>
       </c>
       <c r="AB39" s="7" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="AC39" s="7" t="s">
         <v>98</v>
@@ -7839,7 +7847,7 @@
         <v>9</v>
       </c>
       <c r="AK39" s="7" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="AL39" s="10">
         <f>IF(OR(A39="",COUNT(AF39:AJ39)&lt;5),"",ROUND(SUMPRODUCT(AF39:AJ39,Guia!$B$7:$F$7),1))</f>
@@ -7871,22 +7879,22 @@
     </row>
     <row r="40" spans="1:47" ht="32" customHeight="1">
       <c r="A40" s="7" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="E40" s="7" t="s">
         <v>103</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="G40" s="7" t="s">
         <v>105</v>
@@ -7904,7 +7912,7 @@
         <v>109</v>
       </c>
       <c r="L40" s="7" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="M40" s="7" t="s">
         <v>112</v>
@@ -7931,13 +7939,13 @@
         <v>165</v>
       </c>
       <c r="U40" s="7" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="V40" s="7" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="W40" s="7" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="X40" s="17" t="s">
         <v>204</v>
@@ -7946,13 +7954,13 @@
         <v>150</v>
       </c>
       <c r="Z40" s="7" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="AA40" s="16">
         <v>46293</v>
       </c>
       <c r="AB40" s="7" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="AC40" s="7" t="s">
         <v>98</v>
@@ -7977,7 +7985,7 @@
         <v>8</v>
       </c>
       <c r="AK40" s="7" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="AL40" s="10">
         <f>IF(OR(A40="",COUNT(AF40:AJ40)&lt;5),"",ROUND(SUMPRODUCT(AF40:AJ40,Guia!$B$7:$F$7),1))</f>
@@ -8009,22 +8017,22 @@
     </row>
     <row r="41" spans="1:47" ht="32" customHeight="1">
       <c r="A41" s="7" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="E41" s="7" t="s">
         <v>125</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="G41" s="7" t="s">
         <v>105</v>
@@ -8042,7 +8050,7 @@
         <v>236</v>
       </c>
       <c r="L41" s="7" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="M41" s="7" t="s">
         <v>111</v>
@@ -8069,28 +8077,28 @@
         <v>122</v>
       </c>
       <c r="U41" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="V41" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="W41" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="X41" s="7" t="s">
         <v>479</v>
-      </c>
-      <c r="V41" s="7" t="s">
-        <v>480</v>
-      </c>
-      <c r="W41" s="7" t="s">
-        <v>481</v>
-      </c>
-      <c r="X41" s="7" t="s">
-        <v>482</v>
       </c>
       <c r="Y41" s="7" t="s">
         <v>118</v>
       </c>
       <c r="Z41" s="7" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="AA41" s="16">
         <v>46293</v>
       </c>
       <c r="AB41" s="7" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="AC41" s="7" t="s">
         <v>98</v>
@@ -8115,7 +8123,7 @@
         <v>7</v>
       </c>
       <c r="AK41" s="7" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="AL41" s="10">
         <f>IF(OR(A41="",COUNT(AF41:AJ41)&lt;5),"",ROUND(SUMPRODUCT(AF41:AJ41,Guia!$B$7:$F$7),1))</f>
@@ -8147,22 +8155,22 @@
     </row>
     <row r="42" spans="1:47" ht="32" customHeight="1">
       <c r="A42" s="7" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="E42" s="7" t="s">
         <v>103</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="G42" s="7" t="s">
         <v>105</v>
@@ -8180,7 +8188,7 @@
         <v>109</v>
       </c>
       <c r="L42" s="7" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="M42" s="7" t="s">
         <v>111</v>
@@ -8207,28 +8215,28 @@
         <v>165</v>
       </c>
       <c r="U42" s="7" t="s">
+        <v>499</v>
+      </c>
+      <c r="V42" s="7" t="s">
+        <v>500</v>
+      </c>
+      <c r="W42" s="7" t="s">
+        <v>501</v>
+      </c>
+      <c r="X42" s="7" t="s">
         <v>502</v>
-      </c>
-      <c r="V42" s="7" t="s">
-        <v>503</v>
-      </c>
-      <c r="W42" s="7" t="s">
-        <v>504</v>
-      </c>
-      <c r="X42" s="7" t="s">
-        <v>505</v>
       </c>
       <c r="Y42" s="7" t="s">
         <v>118</v>
       </c>
       <c r="Z42" s="7" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="AA42" s="16">
         <v>46293</v>
       </c>
       <c r="AB42" s="7" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="AC42" s="7" t="s">
         <v>98</v>
@@ -8253,7 +8261,7 @@
         <v>8</v>
       </c>
       <c r="AK42" s="7" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="AL42" s="10">
         <f>IF(OR(A42="",COUNT(AF42:AJ42)&lt;5),"",ROUND(SUMPRODUCT(AF42:AJ42,Guia!$B$7:$F$7),1))</f>
@@ -8285,22 +8293,22 @@
     </row>
     <row r="43" spans="1:47" ht="32" customHeight="1">
       <c r="A43" s="7" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="E43" s="7" t="s">
         <v>103</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="G43" s="7" t="s">
         <v>105</v>
@@ -8318,7 +8326,7 @@
         <v>109</v>
       </c>
       <c r="L43" s="7" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="M43" s="7" t="s">
         <v>122</v>
@@ -8345,13 +8353,13 @@
         <v>165</v>
       </c>
       <c r="U43" s="7" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="V43" s="7" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="W43" s="7" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="X43" s="7" t="s">
         <v>140</v>
@@ -8360,13 +8368,13 @@
         <v>150</v>
       </c>
       <c r="Z43" s="7" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="AA43" s="16">
         <v>46293</v>
       </c>
       <c r="AB43" s="7" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="AC43" s="7" t="s">
         <v>98</v>
@@ -8391,7 +8399,7 @@
         <v>9</v>
       </c>
       <c r="AK43" s="7" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="AL43" s="10">
         <f>IF(OR(A43="",COUNT(AF43:AJ43)&lt;5),"",ROUND(SUMPRODUCT(AF43:AJ43,Guia!$B$7:$F$7),1))</f>
@@ -8423,22 +8431,22 @@
     </row>
     <row r="44" spans="1:47" ht="32" customHeight="1">
       <c r="A44" s="7" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="E44" s="7" t="s">
         <v>125</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="G44" s="7" t="s">
         <v>105</v>
@@ -8481,28 +8489,28 @@
         <v>165</v>
       </c>
       <c r="U44" s="7" t="s">
+        <v>513</v>
+      </c>
+      <c r="V44" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="W44" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="X44" s="7" t="s">
         <v>516</v>
-      </c>
-      <c r="V44" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="W44" s="7" t="s">
-        <v>518</v>
-      </c>
-      <c r="X44" s="7" t="s">
-        <v>519</v>
       </c>
       <c r="Y44" s="7" t="s">
         <v>162</v>
       </c>
       <c r="Z44" s="7" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="AA44" s="16">
         <v>46293</v>
       </c>
       <c r="AB44" s="7" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="AC44" s="7" t="s">
         <v>98</v>
@@ -8527,7 +8535,7 @@
         <v>7</v>
       </c>
       <c r="AK44" s="7" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="AL44" s="10">
         <f>IF(OR(A44="",COUNT(AF44:AJ44)&lt;5),"",ROUND(SUMPRODUCT(AF44:AJ44,Guia!$B$7:$F$7),1))</f>
@@ -8559,22 +8567,22 @@
     </row>
     <row r="45" spans="1:47" ht="32" customHeight="1">
       <c r="A45" s="7" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="E45" s="7" t="s">
         <v>125</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="G45" s="7" t="s">
         <v>105</v>
@@ -8592,7 +8600,7 @@
         <v>236</v>
       </c>
       <c r="L45" s="7" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="M45" s="7" t="s">
         <v>111</v>
@@ -8619,28 +8627,28 @@
         <v>122</v>
       </c>
       <c r="U45" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="V45" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="W45" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="X45" s="7" t="s">
         <v>523</v>
-      </c>
-      <c r="V45" s="7" t="s">
-        <v>524</v>
-      </c>
-      <c r="W45" s="7" t="s">
-        <v>525</v>
-      </c>
-      <c r="X45" s="7" t="s">
-        <v>526</v>
       </c>
       <c r="Y45" s="7" t="s">
         <v>118</v>
       </c>
       <c r="Z45" s="7" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="AA45" s="16">
         <v>46293</v>
       </c>
       <c r="AB45" s="7" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="AC45" s="7" t="s">
         <v>98</v>
@@ -8665,7 +8673,7 @@
         <v>7</v>
       </c>
       <c r="AK45" s="7" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="AL45" s="10">
         <f>IF(OR(A45="",COUNT(AF45:AJ45)&lt;5),"",ROUND(SUMPRODUCT(AF45:AJ45,Guia!$B$7:$F$7),1))</f>
@@ -8697,22 +8705,22 @@
     </row>
     <row r="46" spans="1:47" ht="32" customHeight="1">
       <c r="A46" s="7" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="E46" s="7" t="s">
         <v>103</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="G46" s="7" t="s">
         <v>105</v>
@@ -8730,7 +8738,7 @@
         <v>109</v>
       </c>
       <c r="L46" s="7" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="M46" s="7" t="s">
         <v>122</v>
@@ -8757,13 +8765,13 @@
         <v>165</v>
       </c>
       <c r="U46" s="7" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="V46" s="7" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="W46" s="7" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="X46" s="7" t="s">
         <v>140</v>
@@ -8772,13 +8780,13 @@
         <v>150</v>
       </c>
       <c r="Z46" s="7" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="AA46" s="16">
         <v>46293</v>
       </c>
       <c r="AB46" s="7" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="AC46" s="7" t="s">
         <v>98</v>
@@ -8803,7 +8811,7 @@
         <v>7</v>
       </c>
       <c r="AK46" s="7" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="AL46" s="10">
         <f>IF(OR(A46="",COUNT(AF46:AJ46)&lt;5),"",ROUND(SUMPRODUCT(AF46:AJ46,Guia!$B$7:$F$7),1))</f>
@@ -8835,22 +8843,22 @@
     </row>
     <row r="47" spans="1:47" ht="32" customHeight="1">
       <c r="A47" s="7" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>103</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>105</v>
@@ -8868,7 +8876,7 @@
         <v>109</v>
       </c>
       <c r="L47" s="7" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="M47" s="7" t="s">
         <v>122</v>
@@ -8895,37 +8903,37 @@
         <v>165</v>
       </c>
       <c r="U47" s="7" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="V47" s="7" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="W47" s="7" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="X47" s="7" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="Y47" s="7" t="s">
         <v>118</v>
       </c>
       <c r="Z47" s="7" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="AA47" s="16">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="AB47" s="7" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="AC47" s="7" t="s">
         <v>257</v>
       </c>
       <c r="AD47" s="7" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="AE47" s="7" t="s">
-        <v>772</v>
+        <v>258</v>
       </c>
       <c r="AF47" s="9">
         <v>9</v>
@@ -8943,17 +8951,15 @@
         <v>8</v>
       </c>
       <c r="AK47" s="7" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="AL47" s="10">
         <f>IF(OR(A47="",COUNT(AF47:AJ47)&lt;5),"",ROUND(SUMPRODUCT(AF47:AJ47,Guia!$B$7:$F$7),1))</f>
         <v>8.3000000000000007</v>
       </c>
-      <c r="AM47" s="10">
-        <v>8</v>
-      </c>
+      <c r="AM47" s="10"/>
       <c r="AN47" s="10" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="AO47" s="7" t="s">
         <v>122</v>
@@ -8971,30 +8977,30 @@
         <v>122</v>
       </c>
       <c r="AT47" s="7" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="AU47" s="7" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:47" ht="32" customHeight="1">
       <c r="A48" s="7" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="E48" s="7" t="s">
         <v>103</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="G48" s="7" t="s">
         <v>105</v>
@@ -9012,7 +9018,7 @@
         <v>109</v>
       </c>
       <c r="L48" s="7" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="M48" s="7" t="s">
         <v>122</v>
@@ -9039,28 +9045,28 @@
         <v>165</v>
       </c>
       <c r="U48" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="V48" s="7" t="s">
+        <v>556</v>
+      </c>
+      <c r="W48" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="X48" s="7" t="s">
         <v>558</v>
-      </c>
-      <c r="V48" s="7" t="s">
-        <v>559</v>
-      </c>
-      <c r="W48" s="7" t="s">
-        <v>560</v>
-      </c>
-      <c r="X48" s="7" t="s">
-        <v>561</v>
       </c>
       <c r="Y48" s="7" t="s">
         <v>150</v>
       </c>
       <c r="Z48" s="7" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="AA48" s="16">
         <v>46293</v>
       </c>
       <c r="AB48" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="AC48" s="7" t="s">
         <v>98</v>
@@ -9085,7 +9091,7 @@
         <v>8</v>
       </c>
       <c r="AK48" s="7" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="AL48" s="10">
         <f>IF(OR(A48="",COUNT(AF48:AJ48)&lt;5),"",ROUND(SUMPRODUCT(AF48:AJ48,Guia!$B$7:$F$7),1))</f>
@@ -9117,22 +9123,22 @@
     </row>
     <row r="49" spans="1:47" ht="32" customHeight="1">
       <c r="A49" s="7" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="E49" s="7" t="s">
         <v>103</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="G49" s="7" t="s">
         <v>105</v>
@@ -9150,7 +9156,7 @@
         <v>109</v>
       </c>
       <c r="L49" s="7" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="M49" s="7" t="s">
         <v>111</v>
@@ -9177,28 +9183,28 @@
         <v>165</v>
       </c>
       <c r="U49" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="V49" s="7" t="s">
+        <v>564</v>
+      </c>
+      <c r="W49" s="7" t="s">
+        <v>565</v>
+      </c>
+      <c r="X49" s="7" t="s">
         <v>566</v>
-      </c>
-      <c r="V49" s="7" t="s">
-        <v>567</v>
-      </c>
-      <c r="W49" s="7" t="s">
-        <v>568</v>
-      </c>
-      <c r="X49" s="7" t="s">
-        <v>569</v>
       </c>
       <c r="Y49" s="7" t="s">
         <v>118</v>
       </c>
       <c r="Z49" s="7" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="AA49" s="16">
         <v>46293</v>
       </c>
       <c r="AB49" s="7" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="AC49" s="7" t="s">
         <v>98</v>
@@ -9223,7 +9229,7 @@
         <v>7</v>
       </c>
       <c r="AK49" s="7" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="AL49" s="10">
         <f>IF(OR(A49="",COUNT(AF49:AJ49)&lt;5),"",ROUND(SUMPRODUCT(AF49:AJ49,Guia!$B$7:$F$7),1))</f>
@@ -9255,22 +9261,22 @@
     </row>
     <row r="50" spans="1:47" ht="32" customHeight="1">
       <c r="A50" s="7" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="E50" s="7" t="s">
         <v>125</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="G50" s="7" t="s">
         <v>105</v>
@@ -9288,7 +9294,7 @@
         <v>109</v>
       </c>
       <c r="L50" s="7" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="M50" s="7" t="s">
         <v>113</v>
@@ -9315,28 +9321,28 @@
         <v>97</v>
       </c>
       <c r="U50" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="V50" s="7" t="s">
+        <v>572</v>
+      </c>
+      <c r="W50" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="X50" s="7" t="s">
         <v>574</v>
-      </c>
-      <c r="V50" s="7" t="s">
-        <v>575</v>
-      </c>
-      <c r="W50" s="7" t="s">
-        <v>576</v>
-      </c>
-      <c r="X50" s="7" t="s">
-        <v>577</v>
       </c>
       <c r="Y50" s="7" t="s">
         <v>118</v>
       </c>
       <c r="Z50" s="7" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="AA50" s="16">
         <v>46293</v>
       </c>
       <c r="AB50" s="7" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="AC50" s="7" t="s">
         <v>98</v>
@@ -9361,7 +9367,7 @@
         <v>7</v>
       </c>
       <c r="AK50" s="7" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="AL50" s="10">
         <f>IF(OR(A50="",COUNT(AF50:AJ50)&lt;5),"",ROUND(SUMPRODUCT(AF50:AJ50,Guia!$B$7:$F$7),1))</f>
@@ -9393,28 +9399,28 @@
     </row>
     <row r="51" spans="1:47" ht="32" customHeight="1">
       <c r="A51" s="7" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="E51" s="7" t="s">
         <v>125</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="G51" s="7" t="s">
         <v>105</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="I51" s="7" t="s">
         <v>107</v>
@@ -9426,7 +9432,7 @@
         <v>190</v>
       </c>
       <c r="L51" s="7" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="M51" s="7" t="s">
         <v>111</v>
@@ -9453,28 +9459,28 @@
         <v>165</v>
       </c>
       <c r="U51" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="V51" s="7" t="s">
+        <v>580</v>
+      </c>
+      <c r="W51" s="7" t="s">
+        <v>581</v>
+      </c>
+      <c r="X51" s="7" t="s">
         <v>582</v>
-      </c>
-      <c r="V51" s="7" t="s">
-        <v>583</v>
-      </c>
-      <c r="W51" s="7" t="s">
-        <v>584</v>
-      </c>
-      <c r="X51" s="7" t="s">
-        <v>585</v>
       </c>
       <c r="Y51" s="7" t="s">
         <v>118</v>
       </c>
       <c r="Z51" s="7" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="AA51" s="16">
         <v>46293</v>
       </c>
       <c r="AB51" s="7" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="AC51" s="7" t="s">
         <v>98</v>
@@ -9499,7 +9505,7 @@
         <v>8</v>
       </c>
       <c r="AK51" s="7" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="AL51" s="10">
         <f>IF(OR(A51="",COUNT(AF51:AJ51)&lt;5),"",ROUND(SUMPRODUCT(AF51:AJ51,Guia!$B$7:$F$7),1))</f>
@@ -9531,22 +9537,22 @@
     </row>
     <row r="52" spans="1:47" ht="32" customHeight="1">
       <c r="A52" s="7" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="E52" s="7" t="s">
         <v>103</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>105</v>
@@ -9564,7 +9570,7 @@
         <v>210</v>
       </c>
       <c r="L52" s="7" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="M52" s="7" t="s">
         <v>111</v>
@@ -9591,28 +9597,28 @@
         <v>165</v>
       </c>
       <c r="U52" s="7" t="s">
+        <v>615</v>
+      </c>
+      <c r="V52" s="7" t="s">
+        <v>616</v>
+      </c>
+      <c r="W52" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="X52" s="7" t="s">
         <v>618</v>
-      </c>
-      <c r="V52" s="7" t="s">
-        <v>619</v>
-      </c>
-      <c r="W52" s="7" t="s">
-        <v>620</v>
-      </c>
-      <c r="X52" s="7" t="s">
-        <v>621</v>
       </c>
       <c r="Y52" s="7" t="s">
         <v>118</v>
       </c>
       <c r="Z52" s="7" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="AA52" s="16">
         <v>46293</v>
       </c>
       <c r="AB52" s="7" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="AC52" s="7" t="s">
         <v>98</v>
@@ -9637,7 +9643,7 @@
         <v>7</v>
       </c>
       <c r="AK52" s="7" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="AL52" s="10">
         <f>IF(OR(A52="",COUNT(AF52:AJ52)&lt;5),"",ROUND(SUMPRODUCT(AF52:AJ52,Guia!$B$7:$F$7),1))</f>
@@ -9669,22 +9675,22 @@
     </row>
     <row r="53" spans="1:47" ht="32" customHeight="1">
       <c r="A53" s="7" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="E53" s="7" t="s">
         <v>125</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="G53" s="7" t="s">
         <v>105</v>
@@ -9702,7 +9708,7 @@
         <v>210</v>
       </c>
       <c r="L53" s="7" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="M53" s="7" t="s">
         <v>111</v>
@@ -9729,35 +9735,37 @@
         <v>165</v>
       </c>
       <c r="U53" s="7" t="s">
+        <v>626</v>
+      </c>
+      <c r="V53" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="W53" s="7" t="s">
+        <v>628</v>
+      </c>
+      <c r="X53" s="7" t="s">
         <v>629</v>
-      </c>
-      <c r="V53" s="7" t="s">
-        <v>630</v>
-      </c>
-      <c r="W53" s="7" t="s">
-        <v>631</v>
-      </c>
-      <c r="X53" s="7" t="s">
-        <v>632</v>
       </c>
       <c r="Y53" s="7" t="s">
         <v>118</v>
       </c>
       <c r="Z53" s="7" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="AA53" s="16">
         <v>46293</v>
       </c>
       <c r="AB53" s="7" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC53" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="AD53" s="7"/>
+        <v>257</v>
+      </c>
+      <c r="AD53" s="7" t="s">
+        <v>775</v>
+      </c>
       <c r="AE53" s="7" t="s">
-        <v>120</v>
+        <v>258</v>
       </c>
       <c r="AF53" s="9">
         <v>8</v>
@@ -9775,7 +9783,7 @@
         <v>7</v>
       </c>
       <c r="AK53" s="7" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="AL53" s="10">
         <f>IF(OR(A53="",COUNT(AF53:AJ53)&lt;5),"",ROUND(SUMPRODUCT(AF53:AJ53,Guia!$B$7:$F$7),1))</f>
@@ -9787,16 +9795,16 @@
         <v>122</v>
       </c>
       <c r="AP53" s="7" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="AQ53" s="7" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="AR53" s="7" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="AS53" s="7" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="AT53" s="7" t="s">
         <v>97</v>
@@ -9807,22 +9815,22 @@
     </row>
     <row r="54" spans="1:47" ht="32" customHeight="1">
       <c r="A54" s="7" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="E54" s="7" t="s">
         <v>125</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="G54" s="7" t="s">
         <v>105</v>
@@ -9837,7 +9845,7 @@
         <v>108</v>
       </c>
       <c r="K54" s="7" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="L54" s="7"/>
       <c r="M54" s="7" t="s">
@@ -9865,28 +9873,28 @@
         <v>165</v>
       </c>
       <c r="U54" s="7" t="s">
+        <v>637</v>
+      </c>
+      <c r="V54" s="7" t="s">
+        <v>638</v>
+      </c>
+      <c r="W54" s="7" t="s">
+        <v>639</v>
+      </c>
+      <c r="X54" s="7" t="s">
         <v>640</v>
-      </c>
-      <c r="V54" s="7" t="s">
-        <v>641</v>
-      </c>
-      <c r="W54" s="7" t="s">
-        <v>642</v>
-      </c>
-      <c r="X54" s="7" t="s">
-        <v>643</v>
       </c>
       <c r="Y54" s="7" t="s">
         <v>118</v>
       </c>
       <c r="Z54" s="7" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="AA54" s="16">
         <v>46293</v>
       </c>
       <c r="AB54" s="7" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="AC54" s="7" t="s">
         <v>98</v>
@@ -9911,7 +9919,7 @@
         <v>7</v>
       </c>
       <c r="AK54" s="7" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="AL54" s="10">
         <f>IF(OR(A54="",COUNT(AF54:AJ54)&lt;5),"",ROUND(SUMPRODUCT(AF54:AJ54,Guia!$B$7:$F$7),1))</f>
@@ -9943,22 +9951,22 @@
     </row>
     <row r="55" spans="1:47" ht="32" customHeight="1">
       <c r="A55" s="7" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="E55" s="7" t="s">
         <v>103</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="G55" s="7" t="s">
         <v>105</v>
@@ -9976,7 +9984,7 @@
         <v>210</v>
       </c>
       <c r="L55" s="7" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="M55" s="7" t="s">
         <v>111</v>
@@ -10003,28 +10011,28 @@
         <v>122</v>
       </c>
       <c r="U55" s="7" t="s">
+        <v>648</v>
+      </c>
+      <c r="V55" s="7" t="s">
+        <v>649</v>
+      </c>
+      <c r="W55" s="7" t="s">
+        <v>650</v>
+      </c>
+      <c r="X55" s="7" t="s">
         <v>651</v>
-      </c>
-      <c r="V55" s="7" t="s">
-        <v>652</v>
-      </c>
-      <c r="W55" s="7" t="s">
-        <v>653</v>
-      </c>
-      <c r="X55" s="7" t="s">
-        <v>654</v>
       </c>
       <c r="Y55" s="7" t="s">
         <v>118</v>
       </c>
       <c r="Z55" s="7" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="AA55" s="16">
         <v>46293</v>
       </c>
       <c r="AB55" s="7" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="AC55" s="7" t="s">
         <v>98</v>
@@ -10049,7 +10057,7 @@
         <v>7</v>
       </c>
       <c r="AK55" s="7" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="AL55" s="10">
         <f>IF(OR(A55="",COUNT(AF55:AJ55)&lt;5),"",ROUND(SUMPRODUCT(AF55:AJ55,Guia!$B$7:$F$7),1))</f>
@@ -10081,22 +10089,22 @@
     </row>
     <row r="56" spans="1:47" ht="32" customHeight="1">
       <c r="A56" s="7" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>125</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="G56" s="7" t="s">
         <v>105</v>
@@ -10114,7 +10122,7 @@
         <v>210</v>
       </c>
       <c r="L56" s="7" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="M56" s="7" t="s">
         <v>111</v>
@@ -10141,35 +10149,35 @@
         <v>165</v>
       </c>
       <c r="U56" s="7" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="V56" s="7" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="W56" s="7" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="X56" s="7" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="Y56" s="7" t="s">
         <v>162</v>
       </c>
       <c r="Z56" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="AA56" s="16">
         <v>46293</v>
       </c>
       <c r="AB56" s="7" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="AC56" s="7" t="s">
         <v>257</v>
       </c>
       <c r="AD56" s="7"/>
       <c r="AE56" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AF56" s="9">
         <v>8</v>
@@ -10187,7 +10195,7 @@
         <v>7</v>
       </c>
       <c r="AK56" s="7" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="AL56" s="10">
         <f>IF(OR(A56="",COUNT(AF56:AJ56)&lt;5),"",ROUND(SUMPRODUCT(AF56:AJ56,Guia!$B$7:$F$7),1))</f>
@@ -10208,7 +10216,7 @@
         <v>122</v>
       </c>
       <c r="AS56" s="7" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="AT56" s="7" t="s">
         <v>97</v>
@@ -10219,28 +10227,28 @@
     </row>
     <row r="57" spans="1:47" ht="32" customHeight="1">
       <c r="A57" s="7" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="G57" s="7" t="s">
         <v>105</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="I57" s="7" t="s">
         <v>107</v>
@@ -10252,7 +10260,7 @@
         <v>210</v>
       </c>
       <c r="L57" s="7" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="M57" s="7" t="s">
         <v>111</v>
@@ -10279,28 +10287,28 @@
         <v>165</v>
       </c>
       <c r="U57" s="7" t="s">
+        <v>673</v>
+      </c>
+      <c r="V57" s="7" t="s">
+        <v>674</v>
+      </c>
+      <c r="W57" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="X57" s="7" t="s">
         <v>676</v>
-      </c>
-      <c r="V57" s="7" t="s">
-        <v>677</v>
-      </c>
-      <c r="W57" s="7" t="s">
-        <v>678</v>
-      </c>
-      <c r="X57" s="7" t="s">
-        <v>679</v>
       </c>
       <c r="Y57" s="7" t="s">
         <v>118</v>
       </c>
       <c r="Z57" s="7" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AA57" s="16">
         <v>46293</v>
       </c>
       <c r="AB57" s="7" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="AC57" s="7" t="s">
         <v>98</v>
@@ -10325,7 +10333,7 @@
         <v>7</v>
       </c>
       <c r="AK57" s="7" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="AL57" s="10">
         <f>IF(OR(A57="",COUNT(AF57:AJ57)&lt;5),"",ROUND(SUMPRODUCT(AF57:AJ57,Guia!$B$7:$F$7),1))</f>
@@ -10357,28 +10365,28 @@
     </row>
     <row r="58" spans="1:47" ht="32" customHeight="1">
       <c r="A58" s="7" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="E58" s="7" t="s">
         <v>103</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="G58" s="7" t="s">
         <v>105</v>
       </c>
       <c r="H58" s="7" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="I58" s="7" t="s">
         <v>107</v>
@@ -10390,7 +10398,7 @@
         <v>109</v>
       </c>
       <c r="L58" s="7" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="M58" s="7" t="s">
         <v>111</v>
@@ -10417,28 +10425,28 @@
         <v>165</v>
       </c>
       <c r="U58" s="7" t="s">
+        <v>684</v>
+      </c>
+      <c r="V58" s="7" t="s">
+        <v>685</v>
+      </c>
+      <c r="W58" s="7" t="s">
+        <v>686</v>
+      </c>
+      <c r="X58" s="7" t="s">
         <v>687</v>
-      </c>
-      <c r="V58" s="7" t="s">
-        <v>688</v>
-      </c>
-      <c r="W58" s="7" t="s">
-        <v>689</v>
-      </c>
-      <c r="X58" s="7" t="s">
-        <v>690</v>
       </c>
       <c r="Y58" s="7" t="s">
         <v>118</v>
       </c>
       <c r="Z58" s="7" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="AA58" s="16">
         <v>46293</v>
       </c>
       <c r="AB58" s="7" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="AC58" s="7" t="s">
         <v>98</v>
@@ -10463,7 +10471,7 @@
         <v>7</v>
       </c>
       <c r="AK58" s="7" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="AL58" s="10">
         <f>IF(OR(A58="",COUNT(AF58:AJ58)&lt;5),"",ROUND(SUMPRODUCT(AF58:AJ58,Guia!$B$7:$F$7),1))</f>
@@ -10495,28 +10503,28 @@
     </row>
     <row r="59" spans="1:47" ht="32" customHeight="1">
       <c r="A59" s="7" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>103</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="G59" s="7" t="s">
         <v>105</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="I59" s="7" t="s">
         <v>107</v>
@@ -10528,7 +10536,7 @@
         <v>109</v>
       </c>
       <c r="L59" s="7" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="M59" s="7" t="s">
         <v>122</v>
@@ -10555,13 +10563,13 @@
         <v>165</v>
       </c>
       <c r="U59" s="7" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="V59" s="7" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="W59" s="7" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="X59" s="17" t="s">
         <v>204</v>
@@ -10570,13 +10578,13 @@
         <v>150</v>
       </c>
       <c r="Z59" s="7" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="AA59" s="16">
         <v>46293</v>
       </c>
       <c r="AB59" s="7" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="AC59" s="7" t="s">
         <v>98</v>
@@ -10601,7 +10609,7 @@
         <v>8</v>
       </c>
       <c r="AK59" s="7" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="AL59" s="10">
         <f>IF(OR(A59="",COUNT(AF59:AJ59)&lt;5),"",ROUND(SUMPRODUCT(AF59:AJ59,Guia!$B$7:$F$7),1))</f>
@@ -10633,28 +10641,28 @@
     </row>
     <row r="60" spans="1:47" ht="32" customHeight="1">
       <c r="A60" s="7" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="E60" s="7" t="s">
         <v>125</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="G60" s="7" t="s">
         <v>105</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="I60" s="7" t="s">
         <v>107</v>
@@ -10666,7 +10674,7 @@
         <v>109</v>
       </c>
       <c r="L60" s="7" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="M60" s="7" t="s">
         <v>122</v>
@@ -10693,13 +10701,13 @@
         <v>165</v>
       </c>
       <c r="U60" s="7" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="V60" s="7" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="W60" s="7" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="X60" s="17" t="s">
         <v>204</v>
@@ -10708,13 +10716,13 @@
         <v>150</v>
       </c>
       <c r="Z60" s="7" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="AA60" s="16">
         <v>46293</v>
       </c>
       <c r="AB60" s="7" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="AC60" s="7" t="s">
         <v>98</v>
@@ -10739,7 +10747,7 @@
         <v>8</v>
       </c>
       <c r="AK60" s="7" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="AL60" s="10">
         <f>IF(OR(A60="",COUNT(AF60:AJ60)&lt;5),"",ROUND(SUMPRODUCT(AF60:AJ60,Guia!$B$7:$F$7),1))</f>
@@ -10771,28 +10779,28 @@
     </row>
     <row r="61" spans="1:47" ht="32" customHeight="1">
       <c r="A61" s="7" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="E61" s="7" t="s">
         <v>103</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="G61" s="7" t="s">
         <v>105</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="I61" s="7" t="s">
         <v>107</v>
@@ -10804,7 +10812,7 @@
         <v>109</v>
       </c>
       <c r="L61" s="7" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="M61" s="7" t="s">
         <v>122</v>
@@ -10831,13 +10839,13 @@
         <v>165</v>
       </c>
       <c r="U61" s="7" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="V61" s="7" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="W61" s="7" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="X61" s="17" t="s">
         <v>204</v>
@@ -10846,13 +10854,13 @@
         <v>150</v>
       </c>
       <c r="Z61" s="7" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="AA61" s="16">
         <v>46293</v>
       </c>
       <c r="AB61" s="7" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="AC61" s="7" t="s">
         <v>98</v>
@@ -10877,7 +10885,7 @@
         <v>8</v>
       </c>
       <c r="AK61" s="7" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="AL61" s="10">
         <f>IF(OR(A61="",COUNT(AF61:AJ61)&lt;5),"",ROUND(SUMPRODUCT(AF61:AJ61,Guia!$B$7:$F$7),1))</f>
@@ -10909,22 +10917,22 @@
     </row>
     <row r="62" spans="1:47" ht="32" customHeight="1">
       <c r="A62" s="7" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="E62" s="7" t="s">
         <v>125</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="G62" s="7" t="s">
         <v>105</v>
@@ -10942,7 +10950,7 @@
         <v>109</v>
       </c>
       <c r="L62" s="7" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="M62" s="7" t="s">
         <v>122</v>
@@ -10969,26 +10977,26 @@
         <v>165</v>
       </c>
       <c r="U62" s="7" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="V62" s="7" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="W62" s="7" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="X62" s="7"/>
       <c r="Y62" s="7" t="s">
         <v>150</v>
       </c>
       <c r="Z62" s="7" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="AA62" s="16">
         <v>46293</v>
       </c>
       <c r="AB62" s="7" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="AC62" s="7" t="s">
         <v>98</v>
@@ -11013,7 +11021,7 @@
         <v>7</v>
       </c>
       <c r="AK62" s="7" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="AL62" s="10">
         <f>IF(OR(A62="",COUNT(AF62:AJ62)&lt;5),"",ROUND(SUMPRODUCT(AF62:AJ62,Guia!$B$7:$F$7),1))</f>
@@ -11045,22 +11053,22 @@
     </row>
     <row r="63" spans="1:47" ht="32" customHeight="1">
       <c r="A63" s="7" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="E63" s="7" t="s">
         <v>103</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="G63" s="7" t="s">
         <v>105</v>
@@ -11078,7 +11086,7 @@
         <v>109</v>
       </c>
       <c r="L63" s="7" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="M63" s="7" t="s">
         <v>122</v>
@@ -11105,26 +11113,26 @@
         <v>165</v>
       </c>
       <c r="U63" s="7" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="V63" s="7" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="W63" s="7" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="X63" s="7"/>
       <c r="Y63" s="7" t="s">
         <v>150</v>
       </c>
       <c r="Z63" s="7" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="AA63" s="16">
         <v>46293</v>
       </c>
       <c r="AB63" s="7" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="AC63" s="7" t="s">
         <v>98</v>
@@ -11149,7 +11157,7 @@
         <v>8</v>
       </c>
       <c r="AK63" s="7" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="AL63" s="10">
         <f>IF(OR(A63="",COUNT(AF63:AJ63)&lt;5),"",ROUND(SUMPRODUCT(AF63:AJ63,Guia!$B$7:$F$7),1))</f>
@@ -11181,16 +11189,16 @@
     </row>
     <row r="64" spans="1:47" ht="32" customHeight="1">
       <c r="A64" s="7" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>103</v>
@@ -11214,7 +11222,7 @@
         <v>190</v>
       </c>
       <c r="L64" s="7" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="M64" s="7" t="s">
         <v>112</v>
@@ -11241,28 +11249,28 @@
         <v>165</v>
       </c>
       <c r="U64" s="7" t="s">
+        <v>742</v>
+      </c>
+      <c r="V64" s="7" t="s">
+        <v>743</v>
+      </c>
+      <c r="W64" s="7" t="s">
+        <v>744</v>
+      </c>
+      <c r="X64" s="7" t="s">
         <v>745</v>
-      </c>
-      <c r="V64" s="7" t="s">
-        <v>746</v>
-      </c>
-      <c r="W64" s="7" t="s">
-        <v>747</v>
-      </c>
-      <c r="X64" s="7" t="s">
-        <v>748</v>
       </c>
       <c r="Y64" s="7" t="s">
         <v>118</v>
       </c>
       <c r="Z64" s="7" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="AA64" s="16">
         <v>46293</v>
       </c>
       <c r="AB64" s="7" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="AC64" s="7" t="s">
         <v>98</v>
@@ -11287,7 +11295,7 @@
         <v>6</v>
       </c>
       <c r="AK64" s="7" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="AL64" s="10">
         <f>IF(OR(A64="",COUNT(AF64:AJ64)&lt;5),"",ROUND(SUMPRODUCT(AF64:AJ64,Guia!$B$7:$F$7),1))</f>
@@ -11319,22 +11327,22 @@
     </row>
     <row r="65" spans="1:47" ht="32" customHeight="1">
       <c r="A65" s="7" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="E65" s="7" t="s">
         <v>125</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="G65" s="7" t="s">
         <v>105</v>
@@ -11377,28 +11385,28 @@
         <v>165</v>
       </c>
       <c r="U65" s="7" t="s">
+        <v>751</v>
+      </c>
+      <c r="V65" s="7" t="s">
+        <v>752</v>
+      </c>
+      <c r="W65" s="7" t="s">
+        <v>753</v>
+      </c>
+      <c r="X65" s="7" t="s">
         <v>754</v>
-      </c>
-      <c r="V65" s="7" t="s">
-        <v>755</v>
-      </c>
-      <c r="W65" s="7" t="s">
-        <v>756</v>
-      </c>
-      <c r="X65" s="7" t="s">
-        <v>757</v>
       </c>
       <c r="Y65" s="7" t="s">
         <v>118</v>
       </c>
       <c r="Z65" s="7" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="AA65" s="16">
         <v>46293</v>
       </c>
       <c r="AB65" s="7" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="AC65" s="7" t="s">
         <v>98</v>
@@ -11423,7 +11431,7 @@
         <v>6</v>
       </c>
       <c r="AK65" s="7" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="AL65" s="10">
         <f>IF(OR(A65="",COUNT(AF65:AJ65)&lt;5),"",ROUND(SUMPRODUCT(AF65:AJ65,Guia!$B$7:$F$7),1))</f>
@@ -11455,22 +11463,22 @@
     </row>
     <row r="66" spans="1:47" ht="32" customHeight="1">
       <c r="A66" s="7" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="E66" s="7" t="s">
         <v>103</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="G66" s="7" t="s">
         <v>105</v>
@@ -11488,7 +11496,7 @@
         <v>190</v>
       </c>
       <c r="L66" s="7" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="M66" s="7" t="s">
         <v>112</v>
@@ -11515,26 +11523,26 @@
         <v>122</v>
       </c>
       <c r="U66" s="7" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="V66" s="7" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="W66" s="7" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="X66" s="7"/>
       <c r="Y66" s="7" t="s">
         <v>150</v>
       </c>
       <c r="Z66" s="7" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="AA66" s="16">
         <v>46293</v>
       </c>
       <c r="AB66" s="7" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="AC66" s="7" t="s">
         <v>98</v>
@@ -11559,7 +11567,7 @@
         <v>7</v>
       </c>
       <c r="AK66" s="7" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="AL66" s="10">
         <f>IF(OR(A66="",COUNT(AF66:AJ66)&lt;5),"",ROUND(SUMPRODUCT(AF66:AJ66,Guia!$B$7:$F$7),1))</f>
